--- a/Lumbee_RIVR_Tech_IRU_Package/06_Review_Materials/05_Grant_Compliance_Checklist.xlsx
+++ b/Lumbee_RIVR_Tech_IRU_Package/06_Review_Materials/05_Grant_Compliance_Checklist.xlsx
@@ -530,6 +530,14 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>Parties: Lumbee Tribe of North Carolina (the “Tribe”) and LREMC Technologies, LLC d/b/a RIVR Tech (“RIVR Tech”)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4"/>
     <row r="5">
       <c r="B5" s="3" t="inlineStr">
         <is>
@@ -565,6 +573,7 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>

--- a/Lumbee_RIVR_Tech_IRU_Package/06_Review_Materials/05_Grant_Compliance_Checklist.xlsx
+++ b/Lumbee_RIVR_Tech_IRU_Package/06_Review_Materials/05_Grant_Compliance_Checklist.xlsx
@@ -533,7 +533,7 @@
     <row r="3">
       <c r="B3" s="9" t="inlineStr">
         <is>
-          <t>Parties: Lumbee Tribe of North Carolina (the “Tribe”) and LREMC Technologies, LLC d/b/a RIVR Tech (“RIVR Tech”)</t>
+          <t>Parties: Lumbee Tribe of North Carolina (the “Lumbee Tribe”) and LREMC Technologies, LLC d/b/a RIVR Tech (“RIVR Tech”)</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
     <row r="6">
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Tracks the TBCP / 2 CFR Part 200 compliance obligations for the Tribe as Recipient (with RIVR Tech flow-downs). Status column has a dropdown: Not Started / In Progress / Complete.</t>
+          <t>Tracks the TBCP / 2 CFR Part 200 compliance obligations for the Lumbee Tribe as Recipient (with RIVR Tech flow-downs). Status column has a dropdown: Not Started / In Progress / Complete.</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Tribe procurement + Grant counsel</t>
+          <t>Lumbee Tribe procurement + Grant counsel</t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Tribe procurement</t>
+          <t>Lumbee Tribe procurement</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Tribe + RIVR</t>
+          <t>Lumbee Tribe + RIVR</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Tribe Finance + auditor</t>
+          <t>Lumbee Tribe Finance + auditor</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
@@ -1005,7 +1005,7 @@
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>Tribe + RIVR</t>
+          <t>Lumbee Tribe + RIVR</t>
         </is>
       </c>
       <c r="D16" s="12" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Tribe + RIVR</t>
+          <t>Lumbee Tribe + RIVR</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>Tribe + RIVR</t>
+          <t>Lumbee Tribe + RIVR</t>
         </is>
       </c>
       <c r="D20" s="12" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>Tribe procurement</t>
+          <t>Lumbee Tribe procurement</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t>Tribe + Grant counsel</t>
+          <t>Lumbee Tribe + Grant counsel</t>
         </is>
       </c>
       <c r="D24" s="12" t="inlineStr">
